--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-25T20:14:26.112Z</t>
+    <t>2026-05-01T17:56:48.142Z</t>
   </si>
   <si>
     <t>The leader in semiconductor test &amp; robotics</t>
